--- a/dataset_t6_grouped/results2/G0/G0_DMSO_W0082F0001T0006Z000C1N58_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G0/G0_DMSO_W0082F0001T0006Z000C1N58_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>73.25209033357255</v>
+        <v>11.90346467920554</v>
       </c>
       <c r="D2" t="n">
-        <v>73.19895789220989</v>
+        <v>11.89483065748411</v>
       </c>
       <c r="E2" t="n">
-        <v>11.76510824846372</v>
+        <v>1.911830090375354</v>
       </c>
       <c r="F2" t="n">
-        <v>11.1061900973172</v>
+        <v>1.804755890814044</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>52.94149609050624</v>
+        <v>8.602993114707264</v>
       </c>
       <c r="D3" t="n">
-        <v>52.87752427284951</v>
+        <v>8.592597694338046</v>
       </c>
       <c r="E3" t="n">
-        <v>11.76510824846372</v>
+        <v>1.911830090375354</v>
       </c>
       <c r="F3" t="n">
-        <v>11.1061900973172</v>
+        <v>1.804755890814044</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>45.24544932825125</v>
+        <v>7.352385515840828</v>
       </c>
       <c r="D4" t="n">
-        <v>45.25094030563846</v>
+        <v>7.35327779966625</v>
       </c>
       <c r="E4" t="n">
-        <v>11.76510824846372</v>
+        <v>1.911830090375354</v>
       </c>
       <c r="F4" t="n">
-        <v>11.1061900973172</v>
+        <v>1.804755890814044</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>42.99303914686129</v>
+        <v>6.986368861364959</v>
       </c>
       <c r="D5" t="n">
-        <v>42.53848135721477</v>
+        <v>6.912503220547401</v>
       </c>
       <c r="E5" t="n">
-        <v>11.76510824846372</v>
+        <v>1.911830090375354</v>
       </c>
       <c r="F5" t="n">
-        <v>11.1061900973172</v>
+        <v>1.804755890814044</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>41.20113049962301</v>
+        <v>6.695183706188739</v>
       </c>
       <c r="D6" t="n">
-        <v>60.54668543192988</v>
+        <v>9.838836382688607</v>
       </c>
       <c r="E6" t="n">
-        <v>11.76510824846372</v>
+        <v>1.911830090375354</v>
       </c>
       <c r="F6" t="n">
-        <v>11.1061900973172</v>
+        <v>1.804755890814044</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
